--- a/diseases/d214/2010-2014.xlsx
+++ b/diseases/d214/2010-2014.xlsx
@@ -6356,7 +6356,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
@@ -6758,7 +6758,7 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK38" t="inlineStr">
@@ -7160,7 +7160,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
@@ -7724,7 +7724,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -8126,7 +8126,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -8528,7 +8528,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -8930,7 +8930,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -9494,7 +9494,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK52" t="inlineStr">
@@ -9896,7 +9896,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK54" t="inlineStr">
@@ -10298,7 +10298,7 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK56" t="inlineStr">
@@ -10700,7 +10700,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK58" t="inlineStr">
@@ -11264,7 +11264,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -11666,7 +11666,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -12068,7 +12068,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -12470,7 +12470,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -12872,7 +12872,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -13436,7 +13436,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK72" t="inlineStr">
@@ -13838,7 +13838,7 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK74" t="inlineStr">
@@ -14240,7 +14240,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK76" t="inlineStr">
@@ -14642,7 +14642,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK78" t="inlineStr">
@@ -15206,7 +15206,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -15608,7 +15608,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -16010,7 +16010,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -16412,7 +16412,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -16976,7 +16976,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK90" t="inlineStr">
@@ -17378,7 +17378,7 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK92" t="inlineStr">
@@ -17780,7 +17780,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK94" t="inlineStr">
@@ -18182,7 +18182,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK96" t="inlineStr">
@@ -18584,7 +18584,7 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK98" t="inlineStr">
@@ -19148,7 +19148,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
@@ -19550,7 +19550,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -19952,7 +19952,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -20354,7 +20354,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
@@ -20918,7 +20918,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK110" t="inlineStr">
@@ -21320,7 +21320,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK112" t="inlineStr">
@@ -21722,7 +21722,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK114" t="inlineStr">
@@ -22124,7 +22124,7 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK116" t="inlineStr">
@@ -22688,7 +22688,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK119" t="inlineStr">
@@ -23090,7 +23090,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">
@@ -23492,7 +23492,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -23894,7 +23894,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK125" t="inlineStr">
@@ -24296,7 +24296,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK127" t="inlineStr">
@@ -24860,7 +24860,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK130" t="inlineStr">
@@ -25262,7 +25262,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK132" t="inlineStr">
@@ -25664,7 +25664,7 @@
       </c>
       <c r="AJ134" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK134" t="inlineStr">
@@ -26066,7 +26066,7 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK136" t="inlineStr">
@@ -26630,7 +26630,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK139" t="inlineStr">
@@ -27032,7 +27032,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK141" t="inlineStr">
@@ -27434,7 +27434,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK143" t="inlineStr">
@@ -27836,7 +27836,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK145" t="inlineStr">
@@ -28400,7 +28400,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK148" t="inlineStr">
@@ -28802,7 +28802,7 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK150" t="inlineStr">
@@ -29204,7 +29204,7 @@
       </c>
       <c r="AJ152" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK152" t="inlineStr">
@@ -29606,7 +29606,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK154" t="inlineStr">
@@ -30008,7 +30008,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK156" t="inlineStr">
@@ -30572,7 +30572,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK159" t="inlineStr">
@@ -30974,7 +30974,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK161" t="inlineStr">
@@ -31376,7 +31376,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK163" t="inlineStr">
@@ -31778,7 +31778,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK165" t="inlineStr">
@@ -32342,7 +32342,7 @@
       </c>
       <c r="AJ168" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK168" t="inlineStr">
@@ -32744,7 +32744,7 @@
       </c>
       <c r="AJ170" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK170" t="inlineStr">
@@ -33146,7 +33146,7 @@
       </c>
       <c r="AJ172" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK172" t="inlineStr">
@@ -33548,7 +33548,7 @@
       </c>
       <c r="AJ174" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK174" t="inlineStr">
@@ -34112,7 +34112,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK177" t="inlineStr">
@@ -34514,7 +34514,7 @@
       </c>
       <c r="AJ179" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK179" t="inlineStr">
@@ -34916,7 +34916,7 @@
       </c>
       <c r="AJ181" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK181" t="inlineStr">
@@ -35318,7 +35318,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK183" t="inlineStr">
@@ -35720,7 +35720,7 @@
       </c>
       <c r="AJ185" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK185" t="inlineStr">
@@ -36284,7 +36284,7 @@
       </c>
       <c r="AJ188" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK188" t="inlineStr">
@@ -36686,7 +36686,7 @@
       </c>
       <c r="AJ190" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK190" t="inlineStr">
@@ -37088,7 +37088,7 @@
       </c>
       <c r="AJ192" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK192" t="inlineStr">
@@ -37490,7 +37490,7 @@
       </c>
       <c r="AJ194" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK194" t="inlineStr">
@@ -38054,7 +38054,7 @@
       </c>
       <c r="AJ197" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK197" t="inlineStr">
@@ -38456,7 +38456,7 @@
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK199" t="inlineStr">
@@ -38858,7 +38858,7 @@
       </c>
       <c r="AJ201" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK201" t="inlineStr">
@@ -39260,7 +39260,7 @@
       </c>
       <c r="AJ203" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK203" t="inlineStr">
@@ -39824,7 +39824,7 @@
       </c>
       <c r="AJ206" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK206" t="inlineStr">
@@ -40226,7 +40226,7 @@
       </c>
       <c r="AJ208" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK208" t="inlineStr">
@@ -40628,7 +40628,7 @@
       </c>
       <c r="AJ210" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK210" t="inlineStr">
@@ -41030,7 +41030,7 @@
       </c>
       <c r="AJ212" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK212" t="inlineStr">
@@ -41432,7 +41432,7 @@
       </c>
       <c r="AJ214" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK214" t="inlineStr">
@@ -41996,7 +41996,7 @@
       </c>
       <c r="AJ217" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK217" t="inlineStr">
@@ -42398,7 +42398,7 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK219" t="inlineStr">
@@ -42800,7 +42800,7 @@
       </c>
       <c r="AJ221" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK221" t="inlineStr">
@@ -43202,7 +43202,7 @@
       </c>
       <c r="AJ223" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK223" t="inlineStr">
@@ -43766,7 +43766,7 @@
       </c>
       <c r="AJ226" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK226" t="inlineStr">
@@ -44168,7 +44168,7 @@
       </c>
       <c r="AJ228" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK228" t="inlineStr">
@@ -44570,7 +44570,7 @@
       </c>
       <c r="AJ230" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK230" t="inlineStr">
@@ -44972,7 +44972,7 @@
       </c>
       <c r="AJ232" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK232" t="inlineStr">
@@ -45536,7 +45536,7 @@
       </c>
       <c r="AJ235" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK235" t="inlineStr">
@@ -45938,7 +45938,7 @@
       </c>
       <c r="AJ237" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK237" t="inlineStr">
@@ -46340,7 +46340,7 @@
       </c>
       <c r="AJ239" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK239" t="inlineStr">
@@ -46742,7 +46742,7 @@
       </c>
       <c r="AJ241" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK241" t="inlineStr">
@@ -47144,7 +47144,7 @@
       </c>
       <c r="AJ243" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK243" t="inlineStr">
@@ -47708,7 +47708,7 @@
       </c>
       <c r="AJ246" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK246" t="inlineStr">
@@ -48110,7 +48110,7 @@
       </c>
       <c r="AJ248" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK248" t="inlineStr">
@@ -48512,7 +48512,7 @@
       </c>
       <c r="AJ250" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK250" t="inlineStr">
@@ -48914,7 +48914,7 @@
       </c>
       <c r="AJ252" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK252" t="inlineStr">
@@ -49478,7 +49478,7 @@
       </c>
       <c r="AJ255" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK255" t="inlineStr">
@@ -49880,7 +49880,7 @@
       </c>
       <c r="AJ257" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK257" t="inlineStr">
@@ -50282,7 +50282,7 @@
       </c>
       <c r="AJ259" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK259" t="inlineStr">
@@ -50684,7 +50684,7 @@
       </c>
       <c r="AJ261" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK261" t="inlineStr">
@@ -51086,7 +51086,7 @@
       </c>
       <c r="AJ263" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK263" t="inlineStr">
@@ -51650,7 +51650,7 @@
       </c>
       <c r="AJ266" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK266" t="inlineStr">
@@ -52052,7 +52052,7 @@
       </c>
       <c r="AJ268" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK268" t="inlineStr">
@@ -52454,7 +52454,7 @@
       </c>
       <c r="AJ270" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK270" t="inlineStr">
@@ -52856,7 +52856,7 @@
       </c>
       <c r="AJ272" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK272" t="inlineStr">
@@ -53420,7 +53420,7 @@
       </c>
       <c r="AJ275" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK275" t="inlineStr">
@@ -53822,7 +53822,7 @@
       </c>
       <c r="AJ277" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK277" t="inlineStr">
@@ -54224,7 +54224,7 @@
       </c>
       <c r="AJ279" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK279" t="inlineStr">
@@ -54626,7 +54626,7 @@
       </c>
       <c r="AJ281" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK281" t="inlineStr">
@@ -55190,7 +55190,7 @@
       </c>
       <c r="AJ284" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK284" t="inlineStr">
@@ -55592,7 +55592,7 @@
       </c>
       <c r="AJ286" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK286" t="inlineStr">
@@ -55994,7 +55994,7 @@
       </c>
       <c r="AJ288" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK288" t="inlineStr">
@@ -56396,7 +56396,7 @@
       </c>
       <c r="AJ290" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK290" t="inlineStr">
@@ -56798,7 +56798,7 @@
       </c>
       <c r="AJ292" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK292" t="inlineStr">
@@ -57362,7 +57362,7 @@
       </c>
       <c r="AJ295" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK295" t="inlineStr">
@@ -57764,7 +57764,7 @@
       </c>
       <c r="AJ297" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK297" t="inlineStr">
@@ -58166,7 +58166,7 @@
       </c>
       <c r="AJ299" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK299" t="inlineStr">
@@ -58568,7 +58568,7 @@
       </c>
       <c r="AJ301" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK301" t="inlineStr">

--- a/diseases/d214/2010-2014.xlsx
+++ b/diseases/d214/2010-2014.xlsx
@@ -6356,7 +6356,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
@@ -6758,7 +6758,7 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK38" t="inlineStr">
@@ -7160,7 +7160,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
@@ -7724,7 +7724,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -8126,7 +8126,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -8528,7 +8528,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -8930,7 +8930,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -9494,7 +9494,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK52" t="inlineStr">
@@ -9896,7 +9896,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK54" t="inlineStr">
@@ -10298,7 +10298,7 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK56" t="inlineStr">
@@ -10700,7 +10700,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK58" t="inlineStr">
@@ -11264,7 +11264,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -11666,7 +11666,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -12068,7 +12068,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -12470,7 +12470,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -12872,7 +12872,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -13436,7 +13436,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK72" t="inlineStr">
@@ -13838,7 +13838,7 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK74" t="inlineStr">
@@ -14240,7 +14240,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK76" t="inlineStr">
@@ -14642,7 +14642,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK78" t="inlineStr">
@@ -15206,7 +15206,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -15608,7 +15608,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -16010,7 +16010,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -16412,7 +16412,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -16976,7 +16976,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK90" t="inlineStr">
@@ -17378,7 +17378,7 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK92" t="inlineStr">
@@ -17780,7 +17780,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK94" t="inlineStr">
@@ -18182,7 +18182,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK96" t="inlineStr">
@@ -18584,7 +18584,7 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK98" t="inlineStr">
@@ -19148,7 +19148,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
@@ -19550,7 +19550,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -19952,7 +19952,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -20354,7 +20354,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
@@ -20918,7 +20918,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK110" t="inlineStr">
@@ -21320,7 +21320,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK112" t="inlineStr">
@@ -21722,7 +21722,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK114" t="inlineStr">
@@ -22124,7 +22124,7 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK116" t="inlineStr">
@@ -22688,7 +22688,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK119" t="inlineStr">
@@ -23090,7 +23090,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">
@@ -23492,7 +23492,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -23894,7 +23894,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK125" t="inlineStr">
@@ -24296,7 +24296,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK127" t="inlineStr">
@@ -24860,7 +24860,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK130" t="inlineStr">
@@ -25262,7 +25262,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK132" t="inlineStr">
@@ -25664,7 +25664,7 @@
       </c>
       <c r="AJ134" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK134" t="inlineStr">
@@ -26066,7 +26066,7 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK136" t="inlineStr">
@@ -26630,7 +26630,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK139" t="inlineStr">
@@ -27032,7 +27032,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK141" t="inlineStr">
@@ -27434,7 +27434,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK143" t="inlineStr">
@@ -27836,7 +27836,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK145" t="inlineStr">
@@ -28400,7 +28400,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK148" t="inlineStr">
@@ -28802,7 +28802,7 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK150" t="inlineStr">
@@ -29204,7 +29204,7 @@
       </c>
       <c r="AJ152" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK152" t="inlineStr">
@@ -29606,7 +29606,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK154" t="inlineStr">
@@ -30008,7 +30008,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK156" t="inlineStr">
@@ -30572,7 +30572,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK159" t="inlineStr">
@@ -30974,7 +30974,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK161" t="inlineStr">
@@ -31376,7 +31376,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK163" t="inlineStr">
@@ -31778,7 +31778,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK165" t="inlineStr">
@@ -32342,7 +32342,7 @@
       </c>
       <c r="AJ168" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK168" t="inlineStr">
@@ -32744,7 +32744,7 @@
       </c>
       <c r="AJ170" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK170" t="inlineStr">
@@ -33146,7 +33146,7 @@
       </c>
       <c r="AJ172" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK172" t="inlineStr">
@@ -33548,7 +33548,7 @@
       </c>
       <c r="AJ174" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK174" t="inlineStr">
@@ -34112,7 +34112,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK177" t="inlineStr">
@@ -34514,7 +34514,7 @@
       </c>
       <c r="AJ179" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK179" t="inlineStr">
@@ -34916,7 +34916,7 @@
       </c>
       <c r="AJ181" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK181" t="inlineStr">
@@ -35318,7 +35318,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK183" t="inlineStr">
@@ -35720,7 +35720,7 @@
       </c>
       <c r="AJ185" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK185" t="inlineStr">
@@ -36284,7 +36284,7 @@
       </c>
       <c r="AJ188" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK188" t="inlineStr">
@@ -36686,7 +36686,7 @@
       </c>
       <c r="AJ190" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK190" t="inlineStr">
@@ -37088,7 +37088,7 @@
       </c>
       <c r="AJ192" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK192" t="inlineStr">
@@ -37490,7 +37490,7 @@
       </c>
       <c r="AJ194" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK194" t="inlineStr">
@@ -38054,7 +38054,7 @@
       </c>
       <c r="AJ197" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK197" t="inlineStr">
@@ -38456,7 +38456,7 @@
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK199" t="inlineStr">
@@ -38858,7 +38858,7 @@
       </c>
       <c r="AJ201" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK201" t="inlineStr">
@@ -39260,7 +39260,7 @@
       </c>
       <c r="AJ203" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK203" t="inlineStr">
@@ -39824,7 +39824,7 @@
       </c>
       <c r="AJ206" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK206" t="inlineStr">
@@ -40226,7 +40226,7 @@
       </c>
       <c r="AJ208" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK208" t="inlineStr">
@@ -40628,7 +40628,7 @@
       </c>
       <c r="AJ210" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK210" t="inlineStr">
@@ -41030,7 +41030,7 @@
       </c>
       <c r="AJ212" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK212" t="inlineStr">
@@ -41432,7 +41432,7 @@
       </c>
       <c r="AJ214" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK214" t="inlineStr">
@@ -41996,7 +41996,7 @@
       </c>
       <c r="AJ217" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK217" t="inlineStr">
@@ -42398,7 +42398,7 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK219" t="inlineStr">
@@ -42800,7 +42800,7 @@
       </c>
       <c r="AJ221" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK221" t="inlineStr">
@@ -43202,7 +43202,7 @@
       </c>
       <c r="AJ223" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK223" t="inlineStr">
@@ -43766,7 +43766,7 @@
       </c>
       <c r="AJ226" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK226" t="inlineStr">
@@ -44168,7 +44168,7 @@
       </c>
       <c r="AJ228" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK228" t="inlineStr">
@@ -44570,7 +44570,7 @@
       </c>
       <c r="AJ230" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK230" t="inlineStr">
@@ -44972,7 +44972,7 @@
       </c>
       <c r="AJ232" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK232" t="inlineStr">
@@ -45536,7 +45536,7 @@
       </c>
       <c r="AJ235" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK235" t="inlineStr">
@@ -45938,7 +45938,7 @@
       </c>
       <c r="AJ237" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK237" t="inlineStr">
@@ -46340,7 +46340,7 @@
       </c>
       <c r="AJ239" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK239" t="inlineStr">
@@ -46742,7 +46742,7 @@
       </c>
       <c r="AJ241" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK241" t="inlineStr">
@@ -47144,7 +47144,7 @@
       </c>
       <c r="AJ243" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK243" t="inlineStr">
@@ -47708,7 +47708,7 @@
       </c>
       <c r="AJ246" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK246" t="inlineStr">
@@ -48110,7 +48110,7 @@
       </c>
       <c r="AJ248" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK248" t="inlineStr">
@@ -48512,7 +48512,7 @@
       </c>
       <c r="AJ250" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK250" t="inlineStr">
@@ -48914,7 +48914,7 @@
       </c>
       <c r="AJ252" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK252" t="inlineStr">
@@ -49478,7 +49478,7 @@
       </c>
       <c r="AJ255" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK255" t="inlineStr">
@@ -49880,7 +49880,7 @@
       </c>
       <c r="AJ257" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK257" t="inlineStr">
@@ -50282,7 +50282,7 @@
       </c>
       <c r="AJ259" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK259" t="inlineStr">
@@ -50684,7 +50684,7 @@
       </c>
       <c r="AJ261" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK261" t="inlineStr">
@@ -51086,7 +51086,7 @@
       </c>
       <c r="AJ263" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK263" t="inlineStr">
@@ -51650,7 +51650,7 @@
       </c>
       <c r="AJ266" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK266" t="inlineStr">
@@ -52052,7 +52052,7 @@
       </c>
       <c r="AJ268" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK268" t="inlineStr">
@@ -52454,7 +52454,7 @@
       </c>
       <c r="AJ270" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK270" t="inlineStr">
@@ -52856,7 +52856,7 @@
       </c>
       <c r="AJ272" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK272" t="inlineStr">
@@ -53420,7 +53420,7 @@
       </c>
       <c r="AJ275" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK275" t="inlineStr">
@@ -53822,7 +53822,7 @@
       </c>
       <c r="AJ277" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK277" t="inlineStr">
@@ -54224,7 +54224,7 @@
       </c>
       <c r="AJ279" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK279" t="inlineStr">
@@ -54626,7 +54626,7 @@
       </c>
       <c r="AJ281" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK281" t="inlineStr">
@@ -55190,7 +55190,7 @@
       </c>
       <c r="AJ284" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK284" t="inlineStr">
@@ -55592,7 +55592,7 @@
       </c>
       <c r="AJ286" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK286" t="inlineStr">
@@ -55994,7 +55994,7 @@
       </c>
       <c r="AJ288" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK288" t="inlineStr">
@@ -56396,7 +56396,7 @@
       </c>
       <c r="AJ290" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK290" t="inlineStr">
@@ -56798,7 +56798,7 @@
       </c>
       <c r="AJ292" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK292" t="inlineStr">
@@ -57362,7 +57362,7 @@
       </c>
       <c r="AJ295" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK295" t="inlineStr">
@@ -57764,7 +57764,7 @@
       </c>
       <c r="AJ297" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK297" t="inlineStr">
@@ -58166,7 +58166,7 @@
       </c>
       <c r="AJ299" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK299" t="inlineStr">
@@ -58568,7 +58568,7 @@
       </c>
       <c r="AJ301" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK301" t="inlineStr">

--- a/diseases/d214/2010-2014.xlsx
+++ b/diseases/d214/2010-2014.xlsx
@@ -6114,9 +6114,6 @@
       <c r="P35" t="n">
         <v>0</v>
       </c>
-      <c r="Q35" t="n">
-        <v>0</v>
-      </c>
       <c r="R35" t="n">
         <v>0</v>
       </c>
@@ -6366,7 +6363,7 @@
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN36" t="b">
@@ -6516,9 +6513,6 @@
       <c r="P37" t="n">
         <v>0</v>
       </c>
-      <c r="Q37" t="n">
-        <v>0</v>
-      </c>
       <c r="R37" t="n">
         <v>0</v>
       </c>
@@ -6768,7 +6762,7 @@
       </c>
       <c r="AM38" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN38" t="b">
@@ -6918,9 +6912,6 @@
       <c r="P39" t="n">
         <v>0</v>
       </c>
-      <c r="Q39" t="n">
-        <v>0</v>
-      </c>
       <c r="R39" t="n">
         <v>0</v>
       </c>
@@ -7170,7 +7161,7 @@
       </c>
       <c r="AM40" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN40" t="b">
@@ -7482,9 +7473,6 @@
       <c r="P42" t="n">
         <v>0</v>
       </c>
-      <c r="Q42" t="n">
-        <v>0</v>
-      </c>
       <c r="R42" t="n">
         <v>0</v>
       </c>
@@ -7734,7 +7722,7 @@
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN43" t="b">
@@ -7884,9 +7872,6 @@
       <c r="P44" t="n">
         <v>0</v>
       </c>
-      <c r="Q44" t="n">
-        <v>0</v>
-      </c>
       <c r="R44" t="n">
         <v>0</v>
       </c>
@@ -8136,7 +8121,7 @@
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN45" t="b">
@@ -8286,9 +8271,6 @@
       <c r="P46" t="n">
         <v>0</v>
       </c>
-      <c r="Q46" t="n">
-        <v>0</v>
-      </c>
       <c r="R46" t="n">
         <v>0</v>
       </c>
@@ -8538,7 +8520,7 @@
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN47" t="b">
@@ -8688,9 +8670,6 @@
       <c r="P48" t="n">
         <v>0</v>
       </c>
-      <c r="Q48" t="n">
-        <v>0</v>
-      </c>
       <c r="R48" t="n">
         <v>0</v>
       </c>
@@ -8940,7 +8919,7 @@
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN49" t="b">
@@ -9252,9 +9231,6 @@
       <c r="P51" t="n">
         <v>0</v>
       </c>
-      <c r="Q51" t="n">
-        <v>0</v>
-      </c>
       <c r="R51" t="n">
         <v>0</v>
       </c>
@@ -9504,7 +9480,7 @@
       </c>
       <c r="AM52" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN52" t="b">
@@ -9654,9 +9630,6 @@
       <c r="P53" t="n">
         <v>0</v>
       </c>
-      <c r="Q53" t="n">
-        <v>0</v>
-      </c>
       <c r="R53" t="n">
         <v>0</v>
       </c>
@@ -9906,7 +9879,7 @@
       </c>
       <c r="AM54" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN54" t="b">
@@ -10056,9 +10029,6 @@
       <c r="P55" t="n">
         <v>0</v>
       </c>
-      <c r="Q55" t="n">
-        <v>0</v>
-      </c>
       <c r="R55" t="n">
         <v>0</v>
       </c>
@@ -10308,7 +10278,7 @@
       </c>
       <c r="AM56" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN56" t="b">
@@ -10458,9 +10428,6 @@
       <c r="P57" t="n">
         <v>0</v>
       </c>
-      <c r="Q57" t="n">
-        <v>0</v>
-      </c>
       <c r="R57" t="n">
         <v>0</v>
       </c>
@@ -10710,7 +10677,7 @@
       </c>
       <c r="AM58" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN58" t="b">
@@ -11022,9 +10989,6 @@
       <c r="P60" t="n">
         <v>0</v>
       </c>
-      <c r="Q60" t="n">
-        <v>0</v>
-      </c>
       <c r="R60" t="n">
         <v>0</v>
       </c>
@@ -11274,7 +11238,7 @@
       </c>
       <c r="AM61" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN61" t="b">
@@ -11424,9 +11388,6 @@
       <c r="P62" t="n">
         <v>0</v>
       </c>
-      <c r="Q62" t="n">
-        <v>0</v>
-      </c>
       <c r="R62" t="n">
         <v>0</v>
       </c>
@@ -11676,7 +11637,7 @@
       </c>
       <c r="AM63" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN63" t="b">
@@ -11826,9 +11787,6 @@
       <c r="P64" t="n">
         <v>0</v>
       </c>
-      <c r="Q64" t="n">
-        <v>0</v>
-      </c>
       <c r="R64" t="n">
         <v>0</v>
       </c>
@@ -12078,7 +12036,7 @@
       </c>
       <c r="AM65" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN65" t="b">
@@ -12228,9 +12186,6 @@
       <c r="P66" t="n">
         <v>0</v>
       </c>
-      <c r="Q66" t="n">
-        <v>0</v>
-      </c>
       <c r="R66" t="n">
         <v>0</v>
       </c>
@@ -12480,7 +12435,7 @@
       </c>
       <c r="AM67" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN67" t="b">
@@ -12630,9 +12585,6 @@
       <c r="P68" t="n">
         <v>0</v>
       </c>
-      <c r="Q68" t="n">
-        <v>0</v>
-      </c>
       <c r="R68" t="n">
         <v>0</v>
       </c>
@@ -12882,7 +12834,7 @@
       </c>
       <c r="AM69" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN69" t="b">
@@ -13194,9 +13146,6 @@
       <c r="P71" t="n">
         <v>0</v>
       </c>
-      <c r="Q71" t="n">
-        <v>0</v>
-      </c>
       <c r="R71" t="n">
         <v>0</v>
       </c>
@@ -13446,7 +13395,7 @@
       </c>
       <c r="AM72" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN72" t="b">
@@ -13596,9 +13545,6 @@
       <c r="P73" t="n">
         <v>0</v>
       </c>
-      <c r="Q73" t="n">
-        <v>0</v>
-      </c>
       <c r="R73" t="n">
         <v>0</v>
       </c>
@@ -13848,7 +13794,7 @@
       </c>
       <c r="AM74" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN74" t="b">
@@ -13998,9 +13944,6 @@
       <c r="P75" t="n">
         <v>0</v>
       </c>
-      <c r="Q75" t="n">
-        <v>0</v>
-      </c>
       <c r="R75" t="n">
         <v>0</v>
       </c>
@@ -14250,7 +14193,7 @@
       </c>
       <c r="AM76" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN76" t="b">
@@ -14400,9 +14343,6 @@
       <c r="P77" t="n">
         <v>0</v>
       </c>
-      <c r="Q77" t="n">
-        <v>0</v>
-      </c>
       <c r="R77" t="n">
         <v>0</v>
       </c>
@@ -14652,7 +14592,7 @@
       </c>
       <c r="AM78" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN78" t="b">
@@ -14964,9 +14904,6 @@
       <c r="P80" t="n">
         <v>0</v>
       </c>
-      <c r="Q80" t="n">
-        <v>0</v>
-      </c>
       <c r="R80" t="n">
         <v>0</v>
       </c>
@@ -15216,7 +15153,7 @@
       </c>
       <c r="AM81" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN81" t="b">
@@ -15366,9 +15303,6 @@
       <c r="P82" t="n">
         <v>0</v>
       </c>
-      <c r="Q82" t="n">
-        <v>0</v>
-      </c>
       <c r="R82" t="n">
         <v>0</v>
       </c>
@@ -15618,7 +15552,7 @@
       </c>
       <c r="AM83" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN83" t="b">
@@ -15768,9 +15702,6 @@
       <c r="P84" t="n">
         <v>0</v>
       </c>
-      <c r="Q84" t="n">
-        <v>0</v>
-      </c>
       <c r="R84" t="n">
         <v>0</v>
       </c>
@@ -16020,7 +15951,7 @@
       </c>
       <c r="AM85" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN85" t="b">
@@ -16170,9 +16101,6 @@
       <c r="P86" t="n">
         <v>0</v>
       </c>
-      <c r="Q86" t="n">
-        <v>0</v>
-      </c>
       <c r="R86" t="n">
         <v>0</v>
       </c>
@@ -16422,7 +16350,7 @@
       </c>
       <c r="AM87" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN87" t="b">
@@ -16734,9 +16662,6 @@
       <c r="P89" t="n">
         <v>0</v>
       </c>
-      <c r="Q89" t="n">
-        <v>0</v>
-      </c>
       <c r="R89" t="n">
         <v>0</v>
       </c>
@@ -16986,7 +16911,7 @@
       </c>
       <c r="AM90" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN90" t="b">
@@ -17136,9 +17061,6 @@
       <c r="P91" t="n">
         <v>0</v>
       </c>
-      <c r="Q91" t="n">
-        <v>0</v>
-      </c>
       <c r="R91" t="n">
         <v>0</v>
       </c>
@@ -17388,7 +17310,7 @@
       </c>
       <c r="AM92" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN92" t="b">
@@ -17538,9 +17460,6 @@
       <c r="P93" t="n">
         <v>0</v>
       </c>
-      <c r="Q93" t="n">
-        <v>0</v>
-      </c>
       <c r="R93" t="n">
         <v>0</v>
       </c>
@@ -17790,7 +17709,7 @@
       </c>
       <c r="AM94" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN94" t="b">
@@ -17940,9 +17859,6 @@
       <c r="P95" t="n">
         <v>0</v>
       </c>
-      <c r="Q95" t="n">
-        <v>0</v>
-      </c>
       <c r="R95" t="n">
         <v>0</v>
       </c>
@@ -18192,7 +18108,7 @@
       </c>
       <c r="AM96" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN96" t="b">
@@ -18342,9 +18258,6 @@
       <c r="P97" t="n">
         <v>0</v>
       </c>
-      <c r="Q97" t="n">
-        <v>0</v>
-      </c>
       <c r="R97" t="n">
         <v>0</v>
       </c>
@@ -18594,7 +18507,7 @@
       </c>
       <c r="AM98" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN98" t="b">
@@ -18906,9 +18819,6 @@
       <c r="P100" t="n">
         <v>0</v>
       </c>
-      <c r="Q100" t="n">
-        <v>0</v>
-      </c>
       <c r="R100" t="n">
         <v>0</v>
       </c>
@@ -19158,7 +19068,7 @@
       </c>
       <c r="AM101" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN101" t="b">
@@ -19308,9 +19218,6 @@
       <c r="P102" t="n">
         <v>0</v>
       </c>
-      <c r="Q102" t="n">
-        <v>0</v>
-      </c>
       <c r="R102" t="n">
         <v>0</v>
       </c>
@@ -19560,7 +19467,7 @@
       </c>
       <c r="AM103" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN103" t="b">
@@ -19710,9 +19617,6 @@
       <c r="P104" t="n">
         <v>0</v>
       </c>
-      <c r="Q104" t="n">
-        <v>0</v>
-      </c>
       <c r="R104" t="n">
         <v>0</v>
       </c>
@@ -19962,7 +19866,7 @@
       </c>
       <c r="AM105" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN105" t="b">
@@ -20112,9 +20016,6 @@
       <c r="P106" t="n">
         <v>0</v>
       </c>
-      <c r="Q106" t="n">
-        <v>0</v>
-      </c>
       <c r="R106" t="n">
         <v>0</v>
       </c>
@@ -20364,7 +20265,7 @@
       </c>
       <c r="AM107" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN107" t="b">
@@ -20676,9 +20577,6 @@
       <c r="P109" t="n">
         <v>0</v>
       </c>
-      <c r="Q109" t="n">
-        <v>0</v>
-      </c>
       <c r="R109" t="n">
         <v>0</v>
       </c>
@@ -20928,7 +20826,7 @@
       </c>
       <c r="AM110" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN110" t="b">
@@ -21078,9 +20976,6 @@
       <c r="P111" t="n">
         <v>0</v>
       </c>
-      <c r="Q111" t="n">
-        <v>0</v>
-      </c>
       <c r="R111" t="n">
         <v>0</v>
       </c>
@@ -21330,7 +21225,7 @@
       </c>
       <c r="AM112" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN112" t="b">
@@ -21480,9 +21375,6 @@
       <c r="P113" t="n">
         <v>0</v>
       </c>
-      <c r="Q113" t="n">
-        <v>0</v>
-      </c>
       <c r="R113" t="n">
         <v>0</v>
       </c>
@@ -21732,7 +21624,7 @@
       </c>
       <c r="AM114" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN114" t="b">
@@ -21882,9 +21774,6 @@
       <c r="P115" t="n">
         <v>0</v>
       </c>
-      <c r="Q115" t="n">
-        <v>0</v>
-      </c>
       <c r="R115" t="n">
         <v>0</v>
       </c>
@@ -22134,7 +22023,7 @@
       </c>
       <c r="AM116" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN116" t="b">
@@ -22446,9 +22335,6 @@
       <c r="P118" t="n">
         <v>0</v>
       </c>
-      <c r="Q118" t="n">
-        <v>0</v>
-      </c>
       <c r="R118" t="n">
         <v>0</v>
       </c>
@@ -22698,7 +22584,7 @@
       </c>
       <c r="AM119" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN119" t="b">
@@ -22848,9 +22734,6 @@
       <c r="P120" t="n">
         <v>0</v>
       </c>
-      <c r="Q120" t="n">
-        <v>0</v>
-      </c>
       <c r="R120" t="n">
         <v>0</v>
       </c>
@@ -23100,7 +22983,7 @@
       </c>
       <c r="AM121" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN121" t="b">
@@ -23250,9 +23133,6 @@
       <c r="P122" t="n">
         <v>0</v>
       </c>
-      <c r="Q122" t="n">
-        <v>0</v>
-      </c>
       <c r="R122" t="n">
         <v>0</v>
       </c>
@@ -23502,7 +23382,7 @@
       </c>
       <c r="AM123" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN123" t="b">
@@ -23652,9 +23532,6 @@
       <c r="P124" t="n">
         <v>0</v>
       </c>
-      <c r="Q124" t="n">
-        <v>0</v>
-      </c>
       <c r="R124" t="n">
         <v>0</v>
       </c>
@@ -23904,7 +23781,7 @@
       </c>
       <c r="AM125" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN125" t="b">
@@ -24054,9 +23931,6 @@
       <c r="P126" t="n">
         <v>0</v>
       </c>
-      <c r="Q126" t="n">
-        <v>0</v>
-      </c>
       <c r="R126" t="n">
         <v>0</v>
       </c>
@@ -24306,7 +24180,7 @@
       </c>
       <c r="AM127" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN127" t="b">
@@ -24618,9 +24492,6 @@
       <c r="P129" t="n">
         <v>0</v>
       </c>
-      <c r="Q129" t="n">
-        <v>0</v>
-      </c>
       <c r="R129" t="n">
         <v>0</v>
       </c>
@@ -24870,7 +24741,7 @@
       </c>
       <c r="AM130" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN130" t="b">
@@ -25020,9 +24891,6 @@
       <c r="P131" t="n">
         <v>0</v>
       </c>
-      <c r="Q131" t="n">
-        <v>0</v>
-      </c>
       <c r="R131" t="n">
         <v>0</v>
       </c>
@@ -25272,7 +25140,7 @@
       </c>
       <c r="AM132" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN132" t="b">
@@ -25422,9 +25290,6 @@
       <c r="P133" t="n">
         <v>0</v>
       </c>
-      <c r="Q133" t="n">
-        <v>0</v>
-      </c>
       <c r="R133" t="n">
         <v>0</v>
       </c>
@@ -25674,7 +25539,7 @@
       </c>
       <c r="AM134" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN134" t="b">
@@ -25824,9 +25689,6 @@
       <c r="P135" t="n">
         <v>0</v>
       </c>
-      <c r="Q135" t="n">
-        <v>0</v>
-      </c>
       <c r="R135" t="n">
         <v>0</v>
       </c>
@@ -26076,7 +25938,7 @@
       </c>
       <c r="AM136" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN136" t="b">
@@ -26388,9 +26250,6 @@
       <c r="P138" t="n">
         <v>0</v>
       </c>
-      <c r="Q138" t="n">
-        <v>0</v>
-      </c>
       <c r="R138" t="n">
         <v>0</v>
       </c>
@@ -26640,7 +26499,7 @@
       </c>
       <c r="AM139" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN139" t="b">
@@ -26790,9 +26649,6 @@
       <c r="P140" t="n">
         <v>0</v>
       </c>
-      <c r="Q140" t="n">
-        <v>0</v>
-      </c>
       <c r="R140" t="n">
         <v>0</v>
       </c>
@@ -27042,7 +26898,7 @@
       </c>
       <c r="AM141" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN141" t="b">
@@ -27192,9 +27048,6 @@
       <c r="P142" t="n">
         <v>0</v>
       </c>
-      <c r="Q142" t="n">
-        <v>0</v>
-      </c>
       <c r="R142" t="n">
         <v>0</v>
       </c>
@@ -27444,7 +27297,7 @@
       </c>
       <c r="AM143" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN143" t="b">
@@ -27594,9 +27447,6 @@
       <c r="P144" t="n">
         <v>0</v>
       </c>
-      <c r="Q144" t="n">
-        <v>0</v>
-      </c>
       <c r="R144" t="n">
         <v>0</v>
       </c>
@@ -27846,7 +27696,7 @@
       </c>
       <c r="AM145" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN145" t="b">
@@ -28158,9 +28008,6 @@
       <c r="P147" t="n">
         <v>0</v>
       </c>
-      <c r="Q147" t="n">
-        <v>0</v>
-      </c>
       <c r="R147" t="n">
         <v>0</v>
       </c>
@@ -28410,7 +28257,7 @@
       </c>
       <c r="AM148" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN148" t="b">
@@ -28560,9 +28407,6 @@
       <c r="P149" t="n">
         <v>0</v>
       </c>
-      <c r="Q149" t="n">
-        <v>0</v>
-      </c>
       <c r="R149" t="n">
         <v>0</v>
       </c>
@@ -28812,7 +28656,7 @@
       </c>
       <c r="AM150" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN150" t="b">
@@ -28962,9 +28806,6 @@
       <c r="P151" t="n">
         <v>0</v>
       </c>
-      <c r="Q151" t="n">
-        <v>0</v>
-      </c>
       <c r="R151" t="n">
         <v>0</v>
       </c>
@@ -29214,7 +29055,7 @@
       </c>
       <c r="AM152" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN152" t="b">
@@ -29364,9 +29205,6 @@
       <c r="P153" t="n">
         <v>0</v>
       </c>
-      <c r="Q153" t="n">
-        <v>0</v>
-      </c>
       <c r="R153" t="n">
         <v>0</v>
       </c>
@@ -29616,7 +29454,7 @@
       </c>
       <c r="AM154" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN154" t="b">
@@ -29766,9 +29604,6 @@
       <c r="P155" t="n">
         <v>0</v>
       </c>
-      <c r="Q155" t="n">
-        <v>0</v>
-      </c>
       <c r="R155" t="n">
         <v>0</v>
       </c>
@@ -30018,7 +29853,7 @@
       </c>
       <c r="AM156" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN156" t="b">
@@ -30330,9 +30165,6 @@
       <c r="P158" t="n">
         <v>0</v>
       </c>
-      <c r="Q158" t="n">
-        <v>0</v>
-      </c>
       <c r="R158" t="n">
         <v>0</v>
       </c>
@@ -30582,7 +30414,7 @@
       </c>
       <c r="AM159" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN159" t="b">
@@ -30732,9 +30564,6 @@
       <c r="P160" t="n">
         <v>0</v>
       </c>
-      <c r="Q160" t="n">
-        <v>0</v>
-      </c>
       <c r="R160" t="n">
         <v>0</v>
       </c>
@@ -30984,7 +30813,7 @@
       </c>
       <c r="AM161" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN161" t="b">
@@ -31134,9 +30963,6 @@
       <c r="P162" t="n">
         <v>0</v>
       </c>
-      <c r="Q162" t="n">
-        <v>0</v>
-      </c>
       <c r="R162" t="n">
         <v>0</v>
       </c>
@@ -31386,7 +31212,7 @@
       </c>
       <c r="AM163" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN163" t="b">
@@ -31536,9 +31362,6 @@
       <c r="P164" t="n">
         <v>0</v>
       </c>
-      <c r="Q164" t="n">
-        <v>0</v>
-      </c>
       <c r="R164" t="n">
         <v>0</v>
       </c>
@@ -31788,7 +31611,7 @@
       </c>
       <c r="AM165" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN165" t="b">
@@ -32100,9 +31923,6 @@
       <c r="P167" t="n">
         <v>0</v>
       </c>
-      <c r="Q167" t="n">
-        <v>0</v>
-      </c>
       <c r="R167" t="n">
         <v>0</v>
       </c>
@@ -32352,7 +32172,7 @@
       </c>
       <c r="AM168" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN168" t="b">
@@ -32502,9 +32322,6 @@
       <c r="P169" t="n">
         <v>0</v>
       </c>
-      <c r="Q169" t="n">
-        <v>0</v>
-      </c>
       <c r="R169" t="n">
         <v>0</v>
       </c>
@@ -32754,7 +32571,7 @@
       </c>
       <c r="AM170" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN170" t="b">
@@ -32904,9 +32721,6 @@
       <c r="P171" t="n">
         <v>0</v>
       </c>
-      <c r="Q171" t="n">
-        <v>0</v>
-      </c>
       <c r="R171" t="n">
         <v>0</v>
       </c>
@@ -33156,7 +32970,7 @@
       </c>
       <c r="AM172" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN172" t="b">
@@ -33306,9 +33120,6 @@
       <c r="P173" t="n">
         <v>0</v>
       </c>
-      <c r="Q173" t="n">
-        <v>0</v>
-      </c>
       <c r="R173" t="n">
         <v>0</v>
       </c>
@@ -33558,7 +33369,7 @@
       </c>
       <c r="AM174" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN174" t="b">
@@ -33870,9 +33681,6 @@
       <c r="P176" t="n">
         <v>0</v>
       </c>
-      <c r="Q176" t="n">
-        <v>0</v>
-      </c>
       <c r="R176" t="n">
         <v>0</v>
       </c>
@@ -34122,7 +33930,7 @@
       </c>
       <c r="AM177" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN177" t="b">
@@ -34272,9 +34080,6 @@
       <c r="P178" t="n">
         <v>0</v>
       </c>
-      <c r="Q178" t="n">
-        <v>0</v>
-      </c>
       <c r="R178" t="n">
         <v>0</v>
       </c>
@@ -34524,7 +34329,7 @@
       </c>
       <c r="AM179" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN179" t="b">
@@ -34674,9 +34479,6 @@
       <c r="P180" t="n">
         <v>0</v>
       </c>
-      <c r="Q180" t="n">
-        <v>0</v>
-      </c>
       <c r="R180" t="n">
         <v>0</v>
       </c>
@@ -34926,7 +34728,7 @@
       </c>
       <c r="AM181" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN181" t="b">
@@ -35076,9 +34878,6 @@
       <c r="P182" t="n">
         <v>0</v>
       </c>
-      <c r="Q182" t="n">
-        <v>0</v>
-      </c>
       <c r="R182" t="n">
         <v>0</v>
       </c>
@@ -35328,7 +35127,7 @@
       </c>
       <c r="AM183" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN183" t="b">
@@ -35478,9 +35277,6 @@
       <c r="P184" t="n">
         <v>0</v>
       </c>
-      <c r="Q184" t="n">
-        <v>0</v>
-      </c>
       <c r="R184" t="n">
         <v>0</v>
       </c>
@@ -35730,7 +35526,7 @@
       </c>
       <c r="AM185" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN185" t="b">
@@ -36042,9 +35838,6 @@
       <c r="P187" t="n">
         <v>0</v>
       </c>
-      <c r="Q187" t="n">
-        <v>0</v>
-      </c>
       <c r="R187" t="n">
         <v>0</v>
       </c>
@@ -36294,7 +36087,7 @@
       </c>
       <c r="AM188" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN188" t="b">
@@ -36444,9 +36237,6 @@
       <c r="P189" t="n">
         <v>0</v>
       </c>
-      <c r="Q189" t="n">
-        <v>0</v>
-      </c>
       <c r="R189" t="n">
         <v>0</v>
       </c>
@@ -36696,7 +36486,7 @@
       </c>
       <c r="AM190" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN190" t="b">
@@ -36846,9 +36636,6 @@
       <c r="P191" t="n">
         <v>0</v>
       </c>
-      <c r="Q191" t="n">
-        <v>0</v>
-      </c>
       <c r="R191" t="n">
         <v>0</v>
       </c>
@@ -37098,7 +36885,7 @@
       </c>
       <c r="AM192" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN192" t="b">
@@ -37248,9 +37035,6 @@
       <c r="P193" t="n">
         <v>0</v>
       </c>
-      <c r="Q193" t="n">
-        <v>0</v>
-      </c>
       <c r="R193" t="n">
         <v>0</v>
       </c>
@@ -37500,7 +37284,7 @@
       </c>
       <c r="AM194" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN194" t="b">
@@ -37812,9 +37596,6 @@
       <c r="P196" t="n">
         <v>0</v>
       </c>
-      <c r="Q196" t="n">
-        <v>0</v>
-      </c>
       <c r="R196" t="n">
         <v>0</v>
       </c>
@@ -38064,7 +37845,7 @@
       </c>
       <c r="AM197" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN197" t="b">
@@ -38214,9 +37995,6 @@
       <c r="P198" t="n">
         <v>0</v>
       </c>
-      <c r="Q198" t="n">
-        <v>0</v>
-      </c>
       <c r="R198" t="n">
         <v>0</v>
       </c>
@@ -38466,7 +38244,7 @@
       </c>
       <c r="AM199" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN199" t="b">
@@ -38616,9 +38394,6 @@
       <c r="P200" t="n">
         <v>0</v>
       </c>
-      <c r="Q200" t="n">
-        <v>0</v>
-      </c>
       <c r="R200" t="n">
         <v>0</v>
       </c>
@@ -38868,7 +38643,7 @@
       </c>
       <c r="AM201" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN201" t="b">
@@ -39018,9 +38793,6 @@
       <c r="P202" t="n">
         <v>0</v>
       </c>
-      <c r="Q202" t="n">
-        <v>0</v>
-      </c>
       <c r="R202" t="n">
         <v>0</v>
       </c>
@@ -39270,7 +39042,7 @@
       </c>
       <c r="AM203" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN203" t="b">
@@ -39582,9 +39354,6 @@
       <c r="P205" t="n">
         <v>0</v>
       </c>
-      <c r="Q205" t="n">
-        <v>0</v>
-      </c>
       <c r="R205" t="n">
         <v>0</v>
       </c>
@@ -39834,7 +39603,7 @@
       </c>
       <c r="AM206" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN206" t="b">
@@ -39984,9 +39753,6 @@
       <c r="P207" t="n">
         <v>0</v>
       </c>
-      <c r="Q207" t="n">
-        <v>0</v>
-      </c>
       <c r="R207" t="n">
         <v>0</v>
       </c>
@@ -40236,7 +40002,7 @@
       </c>
       <c r="AM208" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN208" t="b">
@@ -40386,9 +40152,6 @@
       <c r="P209" t="n">
         <v>0</v>
       </c>
-      <c r="Q209" t="n">
-        <v>0</v>
-      </c>
       <c r="R209" t="n">
         <v>0</v>
       </c>
@@ -40638,7 +40401,7 @@
       </c>
       <c r="AM210" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN210" t="b">
@@ -40788,9 +40551,6 @@
       <c r="P211" t="n">
         <v>0</v>
       </c>
-      <c r="Q211" t="n">
-        <v>0</v>
-      </c>
       <c r="R211" t="n">
         <v>0</v>
       </c>
@@ -41040,7 +40800,7 @@
       </c>
       <c r="AM212" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN212" t="b">
@@ -41190,9 +40950,6 @@
       <c r="P213" t="n">
         <v>0</v>
       </c>
-      <c r="Q213" t="n">
-        <v>0</v>
-      </c>
       <c r="R213" t="n">
         <v>0</v>
       </c>
@@ -41442,7 +41199,7 @@
       </c>
       <c r="AM214" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN214" t="b">
@@ -41754,9 +41511,6 @@
       <c r="P216" t="n">
         <v>0</v>
       </c>
-      <c r="Q216" t="n">
-        <v>0</v>
-      </c>
       <c r="R216" t="n">
         <v>0</v>
       </c>
@@ -42006,7 +41760,7 @@
       </c>
       <c r="AM217" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN217" t="b">
@@ -42156,9 +41910,6 @@
       <c r="P218" t="n">
         <v>0</v>
       </c>
-      <c r="Q218" t="n">
-        <v>0</v>
-      </c>
       <c r="R218" t="n">
         <v>0</v>
       </c>
@@ -42408,7 +42159,7 @@
       </c>
       <c r="AM219" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN219" t="b">
@@ -42558,9 +42309,6 @@
       <c r="P220" t="n">
         <v>0</v>
       </c>
-      <c r="Q220" t="n">
-        <v>0</v>
-      </c>
       <c r="R220" t="n">
         <v>0</v>
       </c>
@@ -42810,7 +42558,7 @@
       </c>
       <c r="AM221" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN221" t="b">
@@ -42960,9 +42708,6 @@
       <c r="P222" t="n">
         <v>0</v>
       </c>
-      <c r="Q222" t="n">
-        <v>0</v>
-      </c>
       <c r="R222" t="n">
         <v>0</v>
       </c>
@@ -43212,7 +42957,7 @@
       </c>
       <c r="AM223" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN223" t="b">
@@ -43524,9 +43269,6 @@
       <c r="P225" t="n">
         <v>0</v>
       </c>
-      <c r="Q225" t="n">
-        <v>0</v>
-      </c>
       <c r="R225" t="n">
         <v>0</v>
       </c>
@@ -43776,7 +43518,7 @@
       </c>
       <c r="AM226" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN226" t="b">
@@ -43926,9 +43668,6 @@
       <c r="P227" t="n">
         <v>0</v>
       </c>
-      <c r="Q227" t="n">
-        <v>0</v>
-      </c>
       <c r="R227" t="n">
         <v>0</v>
       </c>
@@ -44178,7 +43917,7 @@
       </c>
       <c r="AM228" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN228" t="b">
@@ -44328,9 +44067,6 @@
       <c r="P229" t="n">
         <v>0</v>
       </c>
-      <c r="Q229" t="n">
-        <v>0</v>
-      </c>
       <c r="R229" t="n">
         <v>0</v>
       </c>
@@ -44580,7 +44316,7 @@
       </c>
       <c r="AM230" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN230" t="b">
@@ -44730,9 +44466,6 @@
       <c r="P231" t="n">
         <v>0</v>
       </c>
-      <c r="Q231" t="n">
-        <v>0</v>
-      </c>
       <c r="R231" t="n">
         <v>0</v>
       </c>
@@ -44982,7 +44715,7 @@
       </c>
       <c r="AM232" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN232" t="b">
@@ -45294,9 +45027,6 @@
       <c r="P234" t="n">
         <v>0</v>
       </c>
-      <c r="Q234" t="n">
-        <v>0</v>
-      </c>
       <c r="R234" t="n">
         <v>0</v>
       </c>
@@ -45546,7 +45276,7 @@
       </c>
       <c r="AM235" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN235" t="b">
@@ -45696,9 +45426,6 @@
       <c r="P236" t="n">
         <v>0</v>
       </c>
-      <c r="Q236" t="n">
-        <v>0</v>
-      </c>
       <c r="R236" t="n">
         <v>0</v>
       </c>
@@ -45948,7 +45675,7 @@
       </c>
       <c r="AM237" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN237" t="b">
@@ -46098,9 +45825,6 @@
       <c r="P238" t="n">
         <v>0</v>
       </c>
-      <c r="Q238" t="n">
-        <v>0</v>
-      </c>
       <c r="R238" t="n">
         <v>0</v>
       </c>
@@ -46350,7 +46074,7 @@
       </c>
       <c r="AM239" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN239" t="b">
@@ -46500,9 +46224,6 @@
       <c r="P240" t="n">
         <v>0</v>
       </c>
-      <c r="Q240" t="n">
-        <v>0</v>
-      </c>
       <c r="R240" t="n">
         <v>0</v>
       </c>
@@ -46752,7 +46473,7 @@
       </c>
       <c r="AM241" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN241" t="b">
@@ -46902,9 +46623,6 @@
       <c r="P242" t="n">
         <v>0</v>
       </c>
-      <c r="Q242" t="n">
-        <v>0</v>
-      </c>
       <c r="R242" t="n">
         <v>0</v>
       </c>
@@ -47154,7 +46872,7 @@
       </c>
       <c r="AM243" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN243" t="b">
@@ -47466,9 +47184,6 @@
       <c r="P245" t="n">
         <v>0</v>
       </c>
-      <c r="Q245" t="n">
-        <v>0</v>
-      </c>
       <c r="R245" t="n">
         <v>0</v>
       </c>
@@ -47718,7 +47433,7 @@
       </c>
       <c r="AM246" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN246" t="b">
@@ -47868,9 +47583,6 @@
       <c r="P247" t="n">
         <v>0</v>
       </c>
-      <c r="Q247" t="n">
-        <v>0</v>
-      </c>
       <c r="R247" t="n">
         <v>0</v>
       </c>
@@ -48120,7 +47832,7 @@
       </c>
       <c r="AM248" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN248" t="b">
@@ -48270,9 +47982,6 @@
       <c r="P249" t="n">
         <v>0</v>
       </c>
-      <c r="Q249" t="n">
-        <v>0</v>
-      </c>
       <c r="R249" t="n">
         <v>0</v>
       </c>
@@ -48522,7 +48231,7 @@
       </c>
       <c r="AM250" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN250" t="b">
@@ -48672,9 +48381,6 @@
       <c r="P251" t="n">
         <v>0</v>
       </c>
-      <c r="Q251" t="n">
-        <v>0</v>
-      </c>
       <c r="R251" t="n">
         <v>0</v>
       </c>
@@ -48924,7 +48630,7 @@
       </c>
       <c r="AM252" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN252" t="b">
@@ -49236,9 +48942,6 @@
       <c r="P254" t="n">
         <v>0</v>
       </c>
-      <c r="Q254" t="n">
-        <v>0</v>
-      </c>
       <c r="R254" t="n">
         <v>0</v>
       </c>
@@ -49488,7 +49191,7 @@
       </c>
       <c r="AM255" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN255" t="b">
@@ -49638,9 +49341,6 @@
       <c r="P256" t="n">
         <v>0</v>
       </c>
-      <c r="Q256" t="n">
-        <v>0</v>
-      </c>
       <c r="R256" t="n">
         <v>0</v>
       </c>
@@ -49890,7 +49590,7 @@
       </c>
       <c r="AM257" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN257" t="b">
@@ -50040,9 +49740,6 @@
       <c r="P258" t="n">
         <v>0</v>
       </c>
-      <c r="Q258" t="n">
-        <v>0</v>
-      </c>
       <c r="R258" t="n">
         <v>0</v>
       </c>
@@ -50292,7 +49989,7 @@
       </c>
       <c r="AM259" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN259" t="b">
@@ -50442,9 +50139,6 @@
       <c r="P260" t="n">
         <v>0</v>
       </c>
-      <c r="Q260" t="n">
-        <v>0</v>
-      </c>
       <c r="R260" t="n">
         <v>0</v>
       </c>
@@ -50694,7 +50388,7 @@
       </c>
       <c r="AM261" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN261" t="b">
@@ -50844,9 +50538,6 @@
       <c r="P262" t="n">
         <v>0</v>
       </c>
-      <c r="Q262" t="n">
-        <v>0</v>
-      </c>
       <c r="R262" t="n">
         <v>0</v>
       </c>
@@ -51096,7 +50787,7 @@
       </c>
       <c r="AM263" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN263" t="b">
@@ -51408,9 +51099,6 @@
       <c r="P265" t="n">
         <v>0</v>
       </c>
-      <c r="Q265" t="n">
-        <v>0</v>
-      </c>
       <c r="R265" t="n">
         <v>0</v>
       </c>
@@ -51660,7 +51348,7 @@
       </c>
       <c r="AM266" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN266" t="b">
@@ -51810,9 +51498,6 @@
       <c r="P267" t="n">
         <v>0</v>
       </c>
-      <c r="Q267" t="n">
-        <v>0</v>
-      </c>
       <c r="R267" t="n">
         <v>0</v>
       </c>
@@ -52062,7 +51747,7 @@
       </c>
       <c r="AM268" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN268" t="b">
@@ -52212,9 +51897,6 @@
       <c r="P269" t="n">
         <v>0</v>
       </c>
-      <c r="Q269" t="n">
-        <v>0</v>
-      </c>
       <c r="R269" t="n">
         <v>0</v>
       </c>
@@ -52464,7 +52146,7 @@
       </c>
       <c r="AM270" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN270" t="b">
@@ -52614,9 +52296,6 @@
       <c r="P271" t="n">
         <v>0</v>
       </c>
-      <c r="Q271" t="n">
-        <v>0</v>
-      </c>
       <c r="R271" t="n">
         <v>0</v>
       </c>
@@ -52866,7 +52545,7 @@
       </c>
       <c r="AM272" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN272" t="b">
@@ -53178,9 +52857,6 @@
       <c r="P274" t="n">
         <v>0</v>
       </c>
-      <c r="Q274" t="n">
-        <v>0</v>
-      </c>
       <c r="R274" t="n">
         <v>0</v>
       </c>
@@ -53430,7 +53106,7 @@
       </c>
       <c r="AM275" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN275" t="b">
@@ -53580,9 +53256,6 @@
       <c r="P276" t="n">
         <v>0</v>
       </c>
-      <c r="Q276" t="n">
-        <v>0</v>
-      </c>
       <c r="R276" t="n">
         <v>0</v>
       </c>
@@ -53832,7 +53505,7 @@
       </c>
       <c r="AM277" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN277" t="b">
@@ -53982,9 +53655,6 @@
       <c r="P278" t="n">
         <v>0</v>
       </c>
-      <c r="Q278" t="n">
-        <v>0</v>
-      </c>
       <c r="R278" t="n">
         <v>0</v>
       </c>
@@ -54234,7 +53904,7 @@
       </c>
       <c r="AM279" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN279" t="b">
@@ -54384,9 +54054,6 @@
       <c r="P280" t="n">
         <v>0</v>
       </c>
-      <c r="Q280" t="n">
-        <v>0</v>
-      </c>
       <c r="R280" t="n">
         <v>0</v>
       </c>
@@ -54636,7 +54303,7 @@
       </c>
       <c r="AM281" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN281" t="b">
@@ -54948,9 +54615,6 @@
       <c r="P283" t="n">
         <v>0</v>
       </c>
-      <c r="Q283" t="n">
-        <v>0</v>
-      </c>
       <c r="R283" t="n">
         <v>0</v>
       </c>
@@ -55200,7 +54864,7 @@
       </c>
       <c r="AM284" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN284" t="b">
@@ -55350,9 +55014,6 @@
       <c r="P285" t="n">
         <v>0</v>
       </c>
-      <c r="Q285" t="n">
-        <v>0</v>
-      </c>
       <c r="R285" t="n">
         <v>0</v>
       </c>
@@ -55602,7 +55263,7 @@
       </c>
       <c r="AM286" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN286" t="b">
@@ -55752,9 +55413,6 @@
       <c r="P287" t="n">
         <v>0</v>
       </c>
-      <c r="Q287" t="n">
-        <v>0</v>
-      </c>
       <c r="R287" t="n">
         <v>0</v>
       </c>
@@ -56004,7 +55662,7 @@
       </c>
       <c r="AM288" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN288" t="b">
@@ -56154,9 +55812,6 @@
       <c r="P289" t="n">
         <v>0</v>
       </c>
-      <c r="Q289" t="n">
-        <v>0</v>
-      </c>
       <c r="R289" t="n">
         <v>0</v>
       </c>
@@ -56406,7 +56061,7 @@
       </c>
       <c r="AM290" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN290" t="b">
@@ -56556,9 +56211,6 @@
       <c r="P291" t="n">
         <v>0</v>
       </c>
-      <c r="Q291" t="n">
-        <v>0</v>
-      </c>
       <c r="R291" t="n">
         <v>0</v>
       </c>
@@ -56808,7 +56460,7 @@
       </c>
       <c r="AM292" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN292" t="b">
@@ -57120,9 +56772,6 @@
       <c r="P294" t="n">
         <v>0</v>
       </c>
-      <c r="Q294" t="n">
-        <v>0</v>
-      </c>
       <c r="R294" t="n">
         <v>0</v>
       </c>
@@ -57372,7 +57021,7 @@
       </c>
       <c r="AM295" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN295" t="b">
@@ -57522,9 +57171,6 @@
       <c r="P296" t="n">
         <v>0</v>
       </c>
-      <c r="Q296" t="n">
-        <v>0</v>
-      </c>
       <c r="R296" t="n">
         <v>0</v>
       </c>
@@ -57774,7 +57420,7 @@
       </c>
       <c r="AM297" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN297" t="b">
@@ -57924,9 +57570,6 @@
       <c r="P298" t="n">
         <v>0</v>
       </c>
-      <c r="Q298" t="n">
-        <v>0</v>
-      </c>
       <c r="R298" t="n">
         <v>0</v>
       </c>
@@ -58176,7 +57819,7 @@
       </c>
       <c r="AM299" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN299" t="b">
@@ -58326,9 +57969,6 @@
       <c r="P300" t="n">
         <v>0</v>
       </c>
-      <c r="Q300" t="n">
-        <v>0</v>
-      </c>
       <c r="R300" t="n">
         <v>0</v>
       </c>
@@ -58578,7 +58218,7 @@
       </c>
       <c r="AM301" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN301" t="b">

--- a/diseases/d214/2010-2014.xlsx
+++ b/diseases/d214/2010-2014.xlsx
@@ -6353,7 +6353,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
@@ -6752,7 +6752,7 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK38" t="inlineStr">
@@ -7151,7 +7151,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
@@ -7712,7 +7712,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -8111,7 +8111,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -8510,7 +8510,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -8909,7 +8909,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -9470,7 +9470,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK52" t="inlineStr">
@@ -9869,7 +9869,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK54" t="inlineStr">
@@ -10268,7 +10268,7 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK56" t="inlineStr">
@@ -10667,7 +10667,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK58" t="inlineStr">
@@ -11228,7 +11228,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -11627,7 +11627,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -12026,7 +12026,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -12425,7 +12425,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -12824,7 +12824,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -13385,7 +13385,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK72" t="inlineStr">
@@ -13784,7 +13784,7 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK74" t="inlineStr">
@@ -14183,7 +14183,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK76" t="inlineStr">
@@ -14582,7 +14582,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK78" t="inlineStr">
@@ -15143,7 +15143,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -15542,7 +15542,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -15941,7 +15941,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -16340,7 +16340,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -16901,7 +16901,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK90" t="inlineStr">
@@ -17300,7 +17300,7 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK92" t="inlineStr">
@@ -17699,7 +17699,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK94" t="inlineStr">
@@ -18098,7 +18098,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK96" t="inlineStr">
@@ -18497,7 +18497,7 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK98" t="inlineStr">
@@ -19058,7 +19058,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
@@ -19457,7 +19457,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -19856,7 +19856,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -20255,7 +20255,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
@@ -20816,7 +20816,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK110" t="inlineStr">
@@ -21215,7 +21215,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK112" t="inlineStr">
@@ -21614,7 +21614,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK114" t="inlineStr">
@@ -22013,7 +22013,7 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK116" t="inlineStr">
@@ -22574,7 +22574,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK119" t="inlineStr">
@@ -22973,7 +22973,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">
@@ -23372,7 +23372,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -23771,7 +23771,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK125" t="inlineStr">
@@ -24170,7 +24170,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK127" t="inlineStr">
@@ -24731,7 +24731,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK130" t="inlineStr">
@@ -25130,7 +25130,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK132" t="inlineStr">
@@ -25529,7 +25529,7 @@
       </c>
       <c r="AJ134" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK134" t="inlineStr">
@@ -25928,7 +25928,7 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK136" t="inlineStr">
@@ -26489,7 +26489,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK139" t="inlineStr">
@@ -26888,7 +26888,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK141" t="inlineStr">
@@ -27287,7 +27287,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK143" t="inlineStr">
@@ -27686,7 +27686,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK145" t="inlineStr">
@@ -28247,7 +28247,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK148" t="inlineStr">
@@ -28646,7 +28646,7 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK150" t="inlineStr">
@@ -29045,7 +29045,7 @@
       </c>
       <c r="AJ152" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK152" t="inlineStr">
@@ -29444,7 +29444,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK154" t="inlineStr">
@@ -29843,7 +29843,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK156" t="inlineStr">
@@ -30404,7 +30404,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK159" t="inlineStr">
@@ -30803,7 +30803,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK161" t="inlineStr">
@@ -31202,7 +31202,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK163" t="inlineStr">
@@ -31601,7 +31601,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK165" t="inlineStr">
@@ -32162,7 +32162,7 @@
       </c>
       <c r="AJ168" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK168" t="inlineStr">
@@ -32561,7 +32561,7 @@
       </c>
       <c r="AJ170" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK170" t="inlineStr">
@@ -32960,7 +32960,7 @@
       </c>
       <c r="AJ172" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK172" t="inlineStr">
@@ -33359,7 +33359,7 @@
       </c>
       <c r="AJ174" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK174" t="inlineStr">
@@ -33920,7 +33920,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK177" t="inlineStr">
@@ -34319,7 +34319,7 @@
       </c>
       <c r="AJ179" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK179" t="inlineStr">
@@ -34718,7 +34718,7 @@
       </c>
       <c r="AJ181" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK181" t="inlineStr">
@@ -35117,7 +35117,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK183" t="inlineStr">
@@ -35516,7 +35516,7 @@
       </c>
       <c r="AJ185" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK185" t="inlineStr">
@@ -36077,7 +36077,7 @@
       </c>
       <c r="AJ188" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK188" t="inlineStr">
@@ -36476,7 +36476,7 @@
       </c>
       <c r="AJ190" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK190" t="inlineStr">
@@ -36875,7 +36875,7 @@
       </c>
       <c r="AJ192" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK192" t="inlineStr">
@@ -37274,7 +37274,7 @@
       </c>
       <c r="AJ194" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK194" t="inlineStr">
@@ -37835,7 +37835,7 @@
       </c>
       <c r="AJ197" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK197" t="inlineStr">
@@ -38234,7 +38234,7 @@
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK199" t="inlineStr">
@@ -38633,7 +38633,7 @@
       </c>
       <c r="AJ201" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK201" t="inlineStr">
@@ -39032,7 +39032,7 @@
       </c>
       <c r="AJ203" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK203" t="inlineStr">
@@ -39593,7 +39593,7 @@
       </c>
       <c r="AJ206" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK206" t="inlineStr">
@@ -39992,7 +39992,7 @@
       </c>
       <c r="AJ208" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK208" t="inlineStr">
@@ -40391,7 +40391,7 @@
       </c>
       <c r="AJ210" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK210" t="inlineStr">
@@ -40790,7 +40790,7 @@
       </c>
       <c r="AJ212" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK212" t="inlineStr">
@@ -41189,7 +41189,7 @@
       </c>
       <c r="AJ214" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK214" t="inlineStr">
@@ -41750,7 +41750,7 @@
       </c>
       <c r="AJ217" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK217" t="inlineStr">
@@ -42149,7 +42149,7 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK219" t="inlineStr">
@@ -42548,7 +42548,7 @@
       </c>
       <c r="AJ221" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK221" t="inlineStr">
@@ -42947,7 +42947,7 @@
       </c>
       <c r="AJ223" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK223" t="inlineStr">
@@ -43508,7 +43508,7 @@
       </c>
       <c r="AJ226" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK226" t="inlineStr">
@@ -43907,7 +43907,7 @@
       </c>
       <c r="AJ228" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK228" t="inlineStr">
@@ -44306,7 +44306,7 @@
       </c>
       <c r="AJ230" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK230" t="inlineStr">
@@ -44705,7 +44705,7 @@
       </c>
       <c r="AJ232" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK232" t="inlineStr">
@@ -45266,7 +45266,7 @@
       </c>
       <c r="AJ235" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK235" t="inlineStr">
@@ -45665,7 +45665,7 @@
       </c>
       <c r="AJ237" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK237" t="inlineStr">
@@ -46064,7 +46064,7 @@
       </c>
       <c r="AJ239" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK239" t="inlineStr">
@@ -46463,7 +46463,7 @@
       </c>
       <c r="AJ241" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK241" t="inlineStr">
@@ -46862,7 +46862,7 @@
       </c>
       <c r="AJ243" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK243" t="inlineStr">
@@ -47423,7 +47423,7 @@
       </c>
       <c r="AJ246" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK246" t="inlineStr">
@@ -47822,7 +47822,7 @@
       </c>
       <c r="AJ248" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK248" t="inlineStr">
@@ -48221,7 +48221,7 @@
       </c>
       <c r="AJ250" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK250" t="inlineStr">
@@ -48620,7 +48620,7 @@
       </c>
       <c r="AJ252" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK252" t="inlineStr">
@@ -49181,7 +49181,7 @@
       </c>
       <c r="AJ255" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK255" t="inlineStr">
@@ -49580,7 +49580,7 @@
       </c>
       <c r="AJ257" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK257" t="inlineStr">
@@ -49979,7 +49979,7 @@
       </c>
       <c r="AJ259" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK259" t="inlineStr">
@@ -50378,7 +50378,7 @@
       </c>
       <c r="AJ261" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK261" t="inlineStr">
@@ -50777,7 +50777,7 @@
       </c>
       <c r="AJ263" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK263" t="inlineStr">
@@ -51338,7 +51338,7 @@
       </c>
       <c r="AJ266" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK266" t="inlineStr">
@@ -51737,7 +51737,7 @@
       </c>
       <c r="AJ268" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK268" t="inlineStr">
@@ -52136,7 +52136,7 @@
       </c>
       <c r="AJ270" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK270" t="inlineStr">
@@ -52535,7 +52535,7 @@
       </c>
       <c r="AJ272" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK272" t="inlineStr">
@@ -53096,7 +53096,7 @@
       </c>
       <c r="AJ275" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK275" t="inlineStr">
@@ -53495,7 +53495,7 @@
       </c>
       <c r="AJ277" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK277" t="inlineStr">
@@ -53894,7 +53894,7 @@
       </c>
       <c r="AJ279" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK279" t="inlineStr">
@@ -54293,7 +54293,7 @@
       </c>
       <c r="AJ281" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK281" t="inlineStr">
@@ -54854,7 +54854,7 @@
       </c>
       <c r="AJ284" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK284" t="inlineStr">
@@ -55253,7 +55253,7 @@
       </c>
       <c r="AJ286" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK286" t="inlineStr">
@@ -55652,7 +55652,7 @@
       </c>
       <c r="AJ288" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK288" t="inlineStr">
@@ -56051,7 +56051,7 @@
       </c>
       <c r="AJ290" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK290" t="inlineStr">
@@ -56450,7 +56450,7 @@
       </c>
       <c r="AJ292" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK292" t="inlineStr">
@@ -57011,7 +57011,7 @@
       </c>
       <c r="AJ295" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK295" t="inlineStr">
@@ -57410,7 +57410,7 @@
       </c>
       <c r="AJ297" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK297" t="inlineStr">
@@ -57809,7 +57809,7 @@
       </c>
       <c r="AJ299" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK299" t="inlineStr">
@@ -58208,7 +58208,7 @@
       </c>
       <c r="AJ301" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK301" t="inlineStr">

--- a/diseases/d214/2010-2014.xlsx
+++ b/diseases/d214/2010-2014.xlsx
@@ -6353,7 +6353,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
@@ -6752,7 +6752,7 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK38" t="inlineStr">
@@ -7151,7 +7151,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
@@ -7712,7 +7712,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -8111,7 +8111,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -8510,7 +8510,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -8909,7 +8909,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -9470,7 +9470,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK52" t="inlineStr">
@@ -9869,7 +9869,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK54" t="inlineStr">
@@ -10268,7 +10268,7 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK56" t="inlineStr">
@@ -10667,7 +10667,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK58" t="inlineStr">
@@ -11228,7 +11228,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -11627,7 +11627,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -12026,7 +12026,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -12425,7 +12425,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -12824,7 +12824,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -13385,7 +13385,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK72" t="inlineStr">
@@ -13784,7 +13784,7 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK74" t="inlineStr">
@@ -14183,7 +14183,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK76" t="inlineStr">
@@ -14582,7 +14582,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK78" t="inlineStr">
@@ -15143,7 +15143,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -15542,7 +15542,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -15941,7 +15941,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -16340,7 +16340,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -16901,7 +16901,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK90" t="inlineStr">
@@ -17300,7 +17300,7 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK92" t="inlineStr">
@@ -17699,7 +17699,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK94" t="inlineStr">
@@ -18098,7 +18098,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK96" t="inlineStr">
@@ -18497,7 +18497,7 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK98" t="inlineStr">
@@ -19058,7 +19058,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
@@ -19457,7 +19457,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -19856,7 +19856,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -20255,7 +20255,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
@@ -20816,7 +20816,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK110" t="inlineStr">
@@ -21215,7 +21215,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK112" t="inlineStr">
@@ -21614,7 +21614,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK114" t="inlineStr">
@@ -22013,7 +22013,7 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK116" t="inlineStr">
@@ -22574,7 +22574,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK119" t="inlineStr">
@@ -22973,7 +22973,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">
@@ -23372,7 +23372,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -23771,7 +23771,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK125" t="inlineStr">
@@ -24170,7 +24170,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK127" t="inlineStr">
@@ -24731,7 +24731,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK130" t="inlineStr">
@@ -25130,7 +25130,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK132" t="inlineStr">
@@ -25529,7 +25529,7 @@
       </c>
       <c r="AJ134" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK134" t="inlineStr">
@@ -25928,7 +25928,7 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK136" t="inlineStr">
@@ -26489,7 +26489,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK139" t="inlineStr">
@@ -26888,7 +26888,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK141" t="inlineStr">
@@ -27287,7 +27287,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK143" t="inlineStr">
@@ -27686,7 +27686,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK145" t="inlineStr">
@@ -28247,7 +28247,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK148" t="inlineStr">
@@ -28646,7 +28646,7 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK150" t="inlineStr">
@@ -29045,7 +29045,7 @@
       </c>
       <c r="AJ152" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK152" t="inlineStr">
@@ -29444,7 +29444,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK154" t="inlineStr">
@@ -29843,7 +29843,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK156" t="inlineStr">
@@ -30404,7 +30404,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK159" t="inlineStr">
@@ -30803,7 +30803,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK161" t="inlineStr">
@@ -31202,7 +31202,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK163" t="inlineStr">
@@ -31601,7 +31601,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK165" t="inlineStr">
@@ -32162,7 +32162,7 @@
       </c>
       <c r="AJ168" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK168" t="inlineStr">
@@ -32561,7 +32561,7 @@
       </c>
       <c r="AJ170" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK170" t="inlineStr">
@@ -32960,7 +32960,7 @@
       </c>
       <c r="AJ172" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK172" t="inlineStr">
@@ -33359,7 +33359,7 @@
       </c>
       <c r="AJ174" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK174" t="inlineStr">
@@ -33920,7 +33920,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK177" t="inlineStr">
@@ -34319,7 +34319,7 @@
       </c>
       <c r="AJ179" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK179" t="inlineStr">
@@ -34718,7 +34718,7 @@
       </c>
       <c r="AJ181" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK181" t="inlineStr">
@@ -35117,7 +35117,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK183" t="inlineStr">
@@ -35516,7 +35516,7 @@
       </c>
       <c r="AJ185" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK185" t="inlineStr">
@@ -36077,7 +36077,7 @@
       </c>
       <c r="AJ188" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK188" t="inlineStr">
@@ -36476,7 +36476,7 @@
       </c>
       <c r="AJ190" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK190" t="inlineStr">
@@ -36875,7 +36875,7 @@
       </c>
       <c r="AJ192" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK192" t="inlineStr">
@@ -37274,7 +37274,7 @@
       </c>
       <c r="AJ194" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK194" t="inlineStr">
@@ -37835,7 +37835,7 @@
       </c>
       <c r="AJ197" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK197" t="inlineStr">
@@ -38234,7 +38234,7 @@
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK199" t="inlineStr">
@@ -38633,7 +38633,7 @@
       </c>
       <c r="AJ201" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK201" t="inlineStr">
@@ -39032,7 +39032,7 @@
       </c>
       <c r="AJ203" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK203" t="inlineStr">
@@ -39593,7 +39593,7 @@
       </c>
       <c r="AJ206" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK206" t="inlineStr">
@@ -39992,7 +39992,7 @@
       </c>
       <c r="AJ208" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK208" t="inlineStr">
@@ -40391,7 +40391,7 @@
       </c>
       <c r="AJ210" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK210" t="inlineStr">
@@ -40790,7 +40790,7 @@
       </c>
       <c r="AJ212" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK212" t="inlineStr">
@@ -41189,7 +41189,7 @@
       </c>
       <c r="AJ214" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK214" t="inlineStr">
@@ -41750,7 +41750,7 @@
       </c>
       <c r="AJ217" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK217" t="inlineStr">
@@ -42149,7 +42149,7 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK219" t="inlineStr">
@@ -42548,7 +42548,7 @@
       </c>
       <c r="AJ221" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK221" t="inlineStr">
@@ -42947,7 +42947,7 @@
       </c>
       <c r="AJ223" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK223" t="inlineStr">
@@ -43508,7 +43508,7 @@
       </c>
       <c r="AJ226" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK226" t="inlineStr">
@@ -43907,7 +43907,7 @@
       </c>
       <c r="AJ228" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK228" t="inlineStr">
@@ -44306,7 +44306,7 @@
       </c>
       <c r="AJ230" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK230" t="inlineStr">
@@ -44705,7 +44705,7 @@
       </c>
       <c r="AJ232" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK232" t="inlineStr">
@@ -45266,7 +45266,7 @@
       </c>
       <c r="AJ235" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK235" t="inlineStr">
@@ -45665,7 +45665,7 @@
       </c>
       <c r="AJ237" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK237" t="inlineStr">
@@ -46064,7 +46064,7 @@
       </c>
       <c r="AJ239" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK239" t="inlineStr">
@@ -46463,7 +46463,7 @@
       </c>
       <c r="AJ241" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK241" t="inlineStr">
@@ -46862,7 +46862,7 @@
       </c>
       <c r="AJ243" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK243" t="inlineStr">
@@ -47423,7 +47423,7 @@
       </c>
       <c r="AJ246" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK246" t="inlineStr">
@@ -47822,7 +47822,7 @@
       </c>
       <c r="AJ248" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK248" t="inlineStr">
@@ -48221,7 +48221,7 @@
       </c>
       <c r="AJ250" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK250" t="inlineStr">
@@ -48620,7 +48620,7 @@
       </c>
       <c r="AJ252" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK252" t="inlineStr">
@@ -49181,7 +49181,7 @@
       </c>
       <c r="AJ255" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK255" t="inlineStr">
@@ -49580,7 +49580,7 @@
       </c>
       <c r="AJ257" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK257" t="inlineStr">
@@ -49979,7 +49979,7 @@
       </c>
       <c r="AJ259" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK259" t="inlineStr">
@@ -50378,7 +50378,7 @@
       </c>
       <c r="AJ261" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK261" t="inlineStr">
@@ -50777,7 +50777,7 @@
       </c>
       <c r="AJ263" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK263" t="inlineStr">
@@ -51338,7 +51338,7 @@
       </c>
       <c r="AJ266" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK266" t="inlineStr">
@@ -51737,7 +51737,7 @@
       </c>
       <c r="AJ268" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK268" t="inlineStr">
@@ -52136,7 +52136,7 @@
       </c>
       <c r="AJ270" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK270" t="inlineStr">
@@ -52535,7 +52535,7 @@
       </c>
       <c r="AJ272" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK272" t="inlineStr">
@@ -53096,7 +53096,7 @@
       </c>
       <c r="AJ275" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK275" t="inlineStr">
@@ -53495,7 +53495,7 @@
       </c>
       <c r="AJ277" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK277" t="inlineStr">
@@ -53894,7 +53894,7 @@
       </c>
       <c r="AJ279" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK279" t="inlineStr">
@@ -54293,7 +54293,7 @@
       </c>
       <c r="AJ281" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK281" t="inlineStr">
@@ -54854,7 +54854,7 @@
       </c>
       <c r="AJ284" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK284" t="inlineStr">
@@ -55253,7 +55253,7 @@
       </c>
       <c r="AJ286" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK286" t="inlineStr">
@@ -55652,7 +55652,7 @@
       </c>
       <c r="AJ288" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK288" t="inlineStr">
@@ -56051,7 +56051,7 @@
       </c>
       <c r="AJ290" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK290" t="inlineStr">
@@ -56450,7 +56450,7 @@
       </c>
       <c r="AJ292" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK292" t="inlineStr">
@@ -57011,7 +57011,7 @@
       </c>
       <c r="AJ295" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK295" t="inlineStr">
@@ -57410,7 +57410,7 @@
       </c>
       <c r="AJ297" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK297" t="inlineStr">
@@ -57809,7 +57809,7 @@
       </c>
       <c r="AJ299" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK299" t="inlineStr">
@@ -58208,7 +58208,7 @@
       </c>
       <c r="AJ301" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK301" t="inlineStr">

--- a/diseases/d214/2010-2014.xlsx
+++ b/diseases/d214/2010-2014.xlsx
@@ -6353,7 +6353,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
@@ -6752,7 +6752,7 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK38" t="inlineStr">
@@ -7151,7 +7151,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
@@ -7712,7 +7712,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -8111,7 +8111,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -8510,7 +8510,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -8909,7 +8909,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -9470,7 +9470,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK52" t="inlineStr">
@@ -9869,7 +9869,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK54" t="inlineStr">
@@ -10268,7 +10268,7 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK56" t="inlineStr">
@@ -10667,7 +10667,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK58" t="inlineStr">
@@ -11228,7 +11228,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -11627,7 +11627,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -12026,7 +12026,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -12425,7 +12425,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -12824,7 +12824,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -13385,7 +13385,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK72" t="inlineStr">
@@ -13784,7 +13784,7 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK74" t="inlineStr">
@@ -14183,7 +14183,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK76" t="inlineStr">
@@ -14582,7 +14582,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK78" t="inlineStr">
@@ -15143,7 +15143,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -15542,7 +15542,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -15941,7 +15941,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -16340,7 +16340,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -16901,7 +16901,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK90" t="inlineStr">
@@ -17300,7 +17300,7 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK92" t="inlineStr">
@@ -17699,7 +17699,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK94" t="inlineStr">
@@ -18098,7 +18098,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK96" t="inlineStr">
@@ -18497,7 +18497,7 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK98" t="inlineStr">
@@ -19058,7 +19058,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
@@ -19457,7 +19457,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -19856,7 +19856,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -20255,7 +20255,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
@@ -20816,7 +20816,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK110" t="inlineStr">
@@ -21215,7 +21215,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK112" t="inlineStr">
@@ -21614,7 +21614,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK114" t="inlineStr">
@@ -22013,7 +22013,7 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK116" t="inlineStr">
@@ -22574,7 +22574,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK119" t="inlineStr">
@@ -22973,7 +22973,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">
@@ -23372,7 +23372,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -23771,7 +23771,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK125" t="inlineStr">
@@ -24170,7 +24170,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK127" t="inlineStr">
@@ -24731,7 +24731,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK130" t="inlineStr">
@@ -25130,7 +25130,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK132" t="inlineStr">
@@ -25529,7 +25529,7 @@
       </c>
       <c r="AJ134" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK134" t="inlineStr">
@@ -25928,7 +25928,7 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK136" t="inlineStr">
@@ -26489,7 +26489,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK139" t="inlineStr">
@@ -26888,7 +26888,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK141" t="inlineStr">
@@ -27287,7 +27287,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK143" t="inlineStr">
@@ -27686,7 +27686,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK145" t="inlineStr">
@@ -28247,7 +28247,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK148" t="inlineStr">
@@ -28646,7 +28646,7 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK150" t="inlineStr">
@@ -29045,7 +29045,7 @@
       </c>
       <c r="AJ152" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK152" t="inlineStr">
@@ -29444,7 +29444,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK154" t="inlineStr">
@@ -29843,7 +29843,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK156" t="inlineStr">
@@ -30404,7 +30404,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK159" t="inlineStr">
@@ -30803,7 +30803,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK161" t="inlineStr">
@@ -31202,7 +31202,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK163" t="inlineStr">
@@ -31601,7 +31601,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK165" t="inlineStr">
@@ -32162,7 +32162,7 @@
       </c>
       <c r="AJ168" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK168" t="inlineStr">
@@ -32561,7 +32561,7 @@
       </c>
       <c r="AJ170" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK170" t="inlineStr">
@@ -32960,7 +32960,7 @@
       </c>
       <c r="AJ172" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK172" t="inlineStr">
@@ -33359,7 +33359,7 @@
       </c>
       <c r="AJ174" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK174" t="inlineStr">
@@ -33920,7 +33920,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK177" t="inlineStr">
@@ -34319,7 +34319,7 @@
       </c>
       <c r="AJ179" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK179" t="inlineStr">
@@ -34718,7 +34718,7 @@
       </c>
       <c r="AJ181" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK181" t="inlineStr">
@@ -35117,7 +35117,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK183" t="inlineStr">
@@ -35516,7 +35516,7 @@
       </c>
       <c r="AJ185" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK185" t="inlineStr">
@@ -36077,7 +36077,7 @@
       </c>
       <c r="AJ188" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK188" t="inlineStr">
@@ -36476,7 +36476,7 @@
       </c>
       <c r="AJ190" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK190" t="inlineStr">
@@ -36875,7 +36875,7 @@
       </c>
       <c r="AJ192" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK192" t="inlineStr">
@@ -37274,7 +37274,7 @@
       </c>
       <c r="AJ194" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK194" t="inlineStr">
@@ -37835,7 +37835,7 @@
       </c>
       <c r="AJ197" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK197" t="inlineStr">
@@ -38234,7 +38234,7 @@
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK199" t="inlineStr">
@@ -38633,7 +38633,7 @@
       </c>
       <c r="AJ201" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK201" t="inlineStr">
@@ -39032,7 +39032,7 @@
       </c>
       <c r="AJ203" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK203" t="inlineStr">
@@ -39593,7 +39593,7 @@
       </c>
       <c r="AJ206" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK206" t="inlineStr">
@@ -39992,7 +39992,7 @@
       </c>
       <c r="AJ208" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK208" t="inlineStr">
@@ -40391,7 +40391,7 @@
       </c>
       <c r="AJ210" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK210" t="inlineStr">
@@ -40790,7 +40790,7 @@
       </c>
       <c r="AJ212" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK212" t="inlineStr">
@@ -41189,7 +41189,7 @@
       </c>
       <c r="AJ214" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK214" t="inlineStr">
@@ -41750,7 +41750,7 @@
       </c>
       <c r="AJ217" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK217" t="inlineStr">
@@ -42149,7 +42149,7 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK219" t="inlineStr">
@@ -42548,7 +42548,7 @@
       </c>
       <c r="AJ221" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK221" t="inlineStr">
@@ -42947,7 +42947,7 @@
       </c>
       <c r="AJ223" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK223" t="inlineStr">
@@ -43508,7 +43508,7 @@
       </c>
       <c r="AJ226" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK226" t="inlineStr">
@@ -43907,7 +43907,7 @@
       </c>
       <c r="AJ228" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK228" t="inlineStr">
@@ -44306,7 +44306,7 @@
       </c>
       <c r="AJ230" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK230" t="inlineStr">
@@ -44705,7 +44705,7 @@
       </c>
       <c r="AJ232" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK232" t="inlineStr">
@@ -45266,7 +45266,7 @@
       </c>
       <c r="AJ235" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK235" t="inlineStr">
@@ -45665,7 +45665,7 @@
       </c>
       <c r="AJ237" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK237" t="inlineStr">
@@ -46064,7 +46064,7 @@
       </c>
       <c r="AJ239" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK239" t="inlineStr">
@@ -46463,7 +46463,7 @@
       </c>
       <c r="AJ241" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK241" t="inlineStr">
@@ -46862,7 +46862,7 @@
       </c>
       <c r="AJ243" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK243" t="inlineStr">
@@ -47423,7 +47423,7 @@
       </c>
       <c r="AJ246" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK246" t="inlineStr">
@@ -47822,7 +47822,7 @@
       </c>
       <c r="AJ248" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK248" t="inlineStr">
@@ -48221,7 +48221,7 @@
       </c>
       <c r="AJ250" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK250" t="inlineStr">
@@ -48620,7 +48620,7 @@
       </c>
       <c r="AJ252" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK252" t="inlineStr">
@@ -49181,7 +49181,7 @@
       </c>
       <c r="AJ255" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK255" t="inlineStr">
@@ -49580,7 +49580,7 @@
       </c>
       <c r="AJ257" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK257" t="inlineStr">
@@ -49979,7 +49979,7 @@
       </c>
       <c r="AJ259" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK259" t="inlineStr">
@@ -50378,7 +50378,7 @@
       </c>
       <c r="AJ261" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK261" t="inlineStr">
@@ -50777,7 +50777,7 @@
       </c>
       <c r="AJ263" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK263" t="inlineStr">
@@ -51338,7 +51338,7 @@
       </c>
       <c r="AJ266" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK266" t="inlineStr">
@@ -51737,7 +51737,7 @@
       </c>
       <c r="AJ268" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK268" t="inlineStr">
@@ -52136,7 +52136,7 @@
       </c>
       <c r="AJ270" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK270" t="inlineStr">
@@ -52535,7 +52535,7 @@
       </c>
       <c r="AJ272" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK272" t="inlineStr">
@@ -53096,7 +53096,7 @@
       </c>
       <c r="AJ275" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK275" t="inlineStr">
@@ -53495,7 +53495,7 @@
       </c>
       <c r="AJ277" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK277" t="inlineStr">
@@ -53894,7 +53894,7 @@
       </c>
       <c r="AJ279" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK279" t="inlineStr">
@@ -54293,7 +54293,7 @@
       </c>
       <c r="AJ281" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK281" t="inlineStr">
@@ -54854,7 +54854,7 @@
       </c>
       <c r="AJ284" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK284" t="inlineStr">
@@ -55253,7 +55253,7 @@
       </c>
       <c r="AJ286" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK286" t="inlineStr">
@@ -55652,7 +55652,7 @@
       </c>
       <c r="AJ288" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK288" t="inlineStr">
@@ -56051,7 +56051,7 @@
       </c>
       <c r="AJ290" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK290" t="inlineStr">
@@ -56450,7 +56450,7 @@
       </c>
       <c r="AJ292" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK292" t="inlineStr">
@@ -57011,7 +57011,7 @@
       </c>
       <c r="AJ295" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK295" t="inlineStr">
@@ -57410,7 +57410,7 @@
       </c>
       <c r="AJ297" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK297" t="inlineStr">
@@ -57809,7 +57809,7 @@
       </c>
       <c r="AJ299" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK299" t="inlineStr">
@@ -58208,7 +58208,7 @@
       </c>
       <c r="AJ301" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK301" t="inlineStr">

--- a/diseases/d214/2010-2014.xlsx
+++ b/diseases/d214/2010-2014.xlsx
@@ -6353,7 +6353,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
@@ -6752,7 +6752,7 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK38" t="inlineStr">
@@ -7151,7 +7151,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
@@ -7712,7 +7712,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -8111,7 +8111,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -8510,7 +8510,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -8909,7 +8909,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -9470,7 +9470,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK52" t="inlineStr">
@@ -9869,7 +9869,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK54" t="inlineStr">
@@ -10268,7 +10268,7 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK56" t="inlineStr">
@@ -10667,7 +10667,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK58" t="inlineStr">
@@ -11228,7 +11228,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -11627,7 +11627,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -12026,7 +12026,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -12425,7 +12425,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -12824,7 +12824,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -13385,7 +13385,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK72" t="inlineStr">
@@ -13784,7 +13784,7 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK74" t="inlineStr">
@@ -14183,7 +14183,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK76" t="inlineStr">
@@ -14582,7 +14582,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK78" t="inlineStr">
@@ -15143,7 +15143,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -15542,7 +15542,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -15941,7 +15941,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -16340,7 +16340,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -16901,7 +16901,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK90" t="inlineStr">
@@ -17300,7 +17300,7 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK92" t="inlineStr">
@@ -17699,7 +17699,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK94" t="inlineStr">
@@ -18098,7 +18098,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK96" t="inlineStr">
@@ -18497,7 +18497,7 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK98" t="inlineStr">
@@ -19058,7 +19058,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
@@ -19457,7 +19457,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -19856,7 +19856,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -20255,7 +20255,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
@@ -20816,7 +20816,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK110" t="inlineStr">
@@ -21215,7 +21215,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK112" t="inlineStr">
@@ -21614,7 +21614,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK114" t="inlineStr">
@@ -22013,7 +22013,7 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK116" t="inlineStr">
@@ -22574,7 +22574,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK119" t="inlineStr">
@@ -22973,7 +22973,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">
@@ -23372,7 +23372,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -23771,7 +23771,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK125" t="inlineStr">
@@ -24170,7 +24170,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK127" t="inlineStr">
@@ -24731,7 +24731,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK130" t="inlineStr">
@@ -25130,7 +25130,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK132" t="inlineStr">
@@ -25529,7 +25529,7 @@
       </c>
       <c r="AJ134" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK134" t="inlineStr">
@@ -25928,7 +25928,7 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK136" t="inlineStr">
@@ -26489,7 +26489,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK139" t="inlineStr">
@@ -26888,7 +26888,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK141" t="inlineStr">
@@ -27287,7 +27287,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK143" t="inlineStr">
@@ -27686,7 +27686,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK145" t="inlineStr">
@@ -28247,7 +28247,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK148" t="inlineStr">
@@ -28646,7 +28646,7 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK150" t="inlineStr">
@@ -29045,7 +29045,7 @@
       </c>
       <c r="AJ152" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK152" t="inlineStr">
@@ -29444,7 +29444,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK154" t="inlineStr">
@@ -29843,7 +29843,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK156" t="inlineStr">
@@ -30404,7 +30404,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK159" t="inlineStr">
@@ -30803,7 +30803,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK161" t="inlineStr">
@@ -31202,7 +31202,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK163" t="inlineStr">
@@ -31601,7 +31601,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK165" t="inlineStr">
@@ -32162,7 +32162,7 @@
       </c>
       <c r="AJ168" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK168" t="inlineStr">
@@ -32561,7 +32561,7 @@
       </c>
       <c r="AJ170" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK170" t="inlineStr">
@@ -32960,7 +32960,7 @@
       </c>
       <c r="AJ172" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK172" t="inlineStr">
@@ -33359,7 +33359,7 @@
       </c>
       <c r="AJ174" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK174" t="inlineStr">
@@ -33920,7 +33920,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK177" t="inlineStr">
@@ -34319,7 +34319,7 @@
       </c>
       <c r="AJ179" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK179" t="inlineStr">
@@ -34718,7 +34718,7 @@
       </c>
       <c r="AJ181" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK181" t="inlineStr">
@@ -35117,7 +35117,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK183" t="inlineStr">
@@ -35516,7 +35516,7 @@
       </c>
       <c r="AJ185" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK185" t="inlineStr">
@@ -36077,7 +36077,7 @@
       </c>
       <c r="AJ188" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK188" t="inlineStr">
@@ -36476,7 +36476,7 @@
       </c>
       <c r="AJ190" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK190" t="inlineStr">
@@ -36875,7 +36875,7 @@
       </c>
       <c r="AJ192" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK192" t="inlineStr">
@@ -37274,7 +37274,7 @@
       </c>
       <c r="AJ194" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK194" t="inlineStr">
@@ -37835,7 +37835,7 @@
       </c>
       <c r="AJ197" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK197" t="inlineStr">
@@ -38234,7 +38234,7 @@
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK199" t="inlineStr">
@@ -38633,7 +38633,7 @@
       </c>
       <c r="AJ201" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK201" t="inlineStr">
@@ -39032,7 +39032,7 @@
       </c>
       <c r="AJ203" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK203" t="inlineStr">
@@ -39593,7 +39593,7 @@
       </c>
       <c r="AJ206" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK206" t="inlineStr">
@@ -39992,7 +39992,7 @@
       </c>
       <c r="AJ208" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK208" t="inlineStr">
@@ -40391,7 +40391,7 @@
       </c>
       <c r="AJ210" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK210" t="inlineStr">
@@ -40790,7 +40790,7 @@
       </c>
       <c r="AJ212" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK212" t="inlineStr">
@@ -41189,7 +41189,7 @@
       </c>
       <c r="AJ214" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK214" t="inlineStr">
@@ -41750,7 +41750,7 @@
       </c>
       <c r="AJ217" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK217" t="inlineStr">
@@ -42149,7 +42149,7 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK219" t="inlineStr">
@@ -42548,7 +42548,7 @@
       </c>
       <c r="AJ221" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK221" t="inlineStr">
@@ -42947,7 +42947,7 @@
       </c>
       <c r="AJ223" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK223" t="inlineStr">
@@ -43508,7 +43508,7 @@
       </c>
       <c r="AJ226" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK226" t="inlineStr">
@@ -43907,7 +43907,7 @@
       </c>
       <c r="AJ228" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK228" t="inlineStr">
@@ -44306,7 +44306,7 @@
       </c>
       <c r="AJ230" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK230" t="inlineStr">
@@ -44705,7 +44705,7 @@
       </c>
       <c r="AJ232" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK232" t="inlineStr">
@@ -45266,7 +45266,7 @@
       </c>
       <c r="AJ235" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK235" t="inlineStr">
@@ -45665,7 +45665,7 @@
       </c>
       <c r="AJ237" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK237" t="inlineStr">
@@ -46064,7 +46064,7 @@
       </c>
       <c r="AJ239" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK239" t="inlineStr">
@@ -46463,7 +46463,7 @@
       </c>
       <c r="AJ241" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK241" t="inlineStr">
@@ -46862,7 +46862,7 @@
       </c>
       <c r="AJ243" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK243" t="inlineStr">
@@ -47423,7 +47423,7 @@
       </c>
       <c r="AJ246" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK246" t="inlineStr">
@@ -47822,7 +47822,7 @@
       </c>
       <c r="AJ248" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK248" t="inlineStr">
@@ -48221,7 +48221,7 @@
       </c>
       <c r="AJ250" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK250" t="inlineStr">
@@ -48620,7 +48620,7 @@
       </c>
       <c r="AJ252" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK252" t="inlineStr">
@@ -49181,7 +49181,7 @@
       </c>
       <c r="AJ255" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK255" t="inlineStr">
@@ -49580,7 +49580,7 @@
       </c>
       <c r="AJ257" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK257" t="inlineStr">
@@ -49979,7 +49979,7 @@
       </c>
       <c r="AJ259" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK259" t="inlineStr">
@@ -50378,7 +50378,7 @@
       </c>
       <c r="AJ261" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK261" t="inlineStr">
@@ -50777,7 +50777,7 @@
       </c>
       <c r="AJ263" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK263" t="inlineStr">
@@ -51338,7 +51338,7 @@
       </c>
       <c r="AJ266" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK266" t="inlineStr">
@@ -51737,7 +51737,7 @@
       </c>
       <c r="AJ268" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK268" t="inlineStr">
@@ -52136,7 +52136,7 @@
       </c>
       <c r="AJ270" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK270" t="inlineStr">
@@ -52535,7 +52535,7 @@
       </c>
       <c r="AJ272" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK272" t="inlineStr">
@@ -53096,7 +53096,7 @@
       </c>
       <c r="AJ275" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK275" t="inlineStr">
@@ -53495,7 +53495,7 @@
       </c>
       <c r="AJ277" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK277" t="inlineStr">
@@ -53894,7 +53894,7 @@
       </c>
       <c r="AJ279" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK279" t="inlineStr">
@@ -54293,7 +54293,7 @@
       </c>
       <c r="AJ281" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK281" t="inlineStr">
@@ -54854,7 +54854,7 @@
       </c>
       <c r="AJ284" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK284" t="inlineStr">
@@ -55253,7 +55253,7 @@
       </c>
       <c r="AJ286" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK286" t="inlineStr">
@@ -55652,7 +55652,7 @@
       </c>
       <c r="AJ288" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK288" t="inlineStr">
@@ -56051,7 +56051,7 @@
       </c>
       <c r="AJ290" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK290" t="inlineStr">
@@ -56450,7 +56450,7 @@
       </c>
       <c r="AJ292" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK292" t="inlineStr">
@@ -57011,7 +57011,7 @@
       </c>
       <c r="AJ295" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK295" t="inlineStr">
@@ -57410,7 +57410,7 @@
       </c>
       <c r="AJ297" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK297" t="inlineStr">
@@ -57809,7 +57809,7 @@
       </c>
       <c r="AJ299" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK299" t="inlineStr">
@@ -58208,7 +58208,7 @@
       </c>
       <c r="AJ301" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK301" t="inlineStr">
